--- a/src/fluorophores/cy5_properties.xlsx
+++ b/src/fluorophores/cy5_properties.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwuerzburg-my.sharepoint.com/personal/vincent_ebert_stud-mail_uni-wuerzburg_de/Documents/GitHub/Photoswitching/src/fluorophores/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_AD4DB114E441178AC67DF44A5610C320683EDF1B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDF55206-A1C9-41ED-B83A-EC0E7509C56E}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="11_AD4DB114E441178AC67DF44A5610C320683EDF1B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93C94ADF-3D06-44DB-8FB2-19CF753EDE20}"/>
   <bookViews>
-    <workbookView xWindow="45972" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="45972" yWindow="4908" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>maximum extinction coefficient [1/(cm M)]</t>
   </si>
@@ -61,6 +61,12 @@
   </si>
   <si>
     <t>quantum yield</t>
+  </si>
+  <si>
+    <t>fret spectral overlap integral</t>
+  </si>
+  <si>
+    <t>fret dipole orientation factor</t>
   </si>
 </sst>
 </file>
@@ -127,10 +133,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -396,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="39.86328125" bestFit="1" customWidth="1"/>
@@ -500,6 +502,25 @@
         <v>1.6999999999999999E-17</v>
       </c>
     </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0.66666599999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="B14" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="597" r:id="rId1"/>

--- a/src/fluorophores/cy5_properties.xlsx
+++ b/src/fluorophores/cy5_properties.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwuerzburg-my.sharepoint.com/personal/vincent_ebert_stud-mail_uni-wuerzburg_de/Documents/GitHub/Photoswitching/src/fluorophores/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="11_AD4DB114E441178AC67DF44A5610C320683EDF1B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93C94ADF-3D06-44DB-8FB2-19CF753EDE20}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="11_AD4DB114E441178AC67DF44A5610C320683EDF1B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFDC76B3-BB45-4A6B-948B-6CCFD77EC489}"/>
   <bookViews>
-    <workbookView xWindow="45972" yWindow="4908" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1620" yWindow="2400" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>maximum extinction coefficient [1/(cm M)]</t>
   </si>
@@ -63,10 +63,45 @@
     <t>quantum yield</t>
   </si>
   <si>
-    <t>fret spectral overlap integral</t>
-  </si>
-  <si>
     <t>fret dipole orientation factor</t>
+  </si>
+  <si>
+    <t>HOMO Fret</t>
+  </si>
+  <si>
+    <t>Cis</t>
+  </si>
+  <si>
+    <t>Triplet</t>
+  </si>
+  <si>
+    <t>OFF</t>
+  </si>
+  <si>
+    <r>
+      <t>fret spectral overlap integrals [nm</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/(cm M)]</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -76,7 +111,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000E+00"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -86,6 +121,14 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -133,6 +176,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -398,15 +445,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:J19"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.86328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="9.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
@@ -414,7 +461,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -430,7 +477,7 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -438,7 +485,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -446,7 +493,7 @@
         <v>1.0000000000000001E-9</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -454,7 +501,7 @@
         <v>830000</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -462,7 +509,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -470,15 +517,15 @@
         <v>96000000</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -486,7 +533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -494,7 +541,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -502,24 +549,54 @@
         <v>1.6999999999999999E-17</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>12</v>
-      </c>
-      <c r="B12" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>13</v>
       </c>
       <c r="B13" s="2">
         <v>0.66666599999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B14" s="2"/>
+    </row>
+    <row r="15" spans="1:10" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="2"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="2">
+        <v>1.55E+16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="2">
+        <v>3E+16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="2">
+        <v>9000000000000000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="2">
+        <v>1000000000000000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
